--- a/foret/Comparaison_modeles.xlsx
+++ b/foret/Comparaison_modeles.xlsx
@@ -8,16 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ingé\3A\Stage\Cervides_Aubrac\Analyse\Analyses_Aubrac\foret\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B3B5AE-083A-4A0D-BAEB-84F31F0AA899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29C7847-BEBD-4412-8AFF-46262B8E0C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{A86A450A-C475-4D34-978B-F5B84E1989D9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="5" xr2:uid="{A86A450A-C475-4D34-978B-F5B84E1989D9}"/>
   </bookViews>
   <sheets>
-    <sheet name="REC_FN_ABROU" sheetId="1" r:id="rId1"/>
-    <sheet name="DIV_HERBACEE_FN_ABROU" sheetId="2" r:id="rId2"/>
-    <sheet name="REC_FN_FECES" sheetId="3" r:id="rId3"/>
+    <sheet name="ABROU_FORET" sheetId="4" r:id="rId1"/>
+    <sheet name="ABROU_HETRAIES" sheetId="5" r:id="rId2"/>
+    <sheet name="ABROU_FEUILLUS" sheetId="6" r:id="rId3"/>
+    <sheet name="REC_FN_ABROU" sheetId="1" r:id="rId4"/>
+    <sheet name="DIV_HERBACEE_FN_ABROU" sheetId="2" r:id="rId5"/>
+    <sheet name="REC_FN_FECES" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="550">
   <si>
     <t>Type</t>
   </si>
@@ -239,13 +242,1476 @@
   </si>
   <si>
     <t>NB_FECES, value = -7.80593, p-value = 0.0066, SE = 2.706249, DF = 36, t-value = -2.8844108</t>
+  </si>
+  <si>
+    <t>Call:</t>
+  </si>
+  <si>
+    <t>model.avg(object = model_logit_dredge, subset = delta &lt;= 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component model call: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">lme.formula(fixed = logit_AMOYj ~ &lt;7 unique rhs&gt;, data = info_placette_aldous_glmm, random = ~1 | ZONE2, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     method = ML, na.action = na.fail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Component models: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">       df  logLik   AICc delta weight</t>
+  </si>
+  <si>
+    <t>45678  11 -179.72 384.31  0.00   0.28</t>
+  </si>
+  <si>
+    <t>5678   10 -181.49 385.34  1.03   0.16</t>
+  </si>
+  <si>
+    <t>345678 12 -179.20 385.83  1.52   0.13</t>
+  </si>
+  <si>
+    <t>4578   10 -181.89 386.14  1.83   0.11</t>
+  </si>
+  <si>
+    <t>145678 12 -179.39 386.21  1.90   0.11</t>
+  </si>
+  <si>
+    <t>4678   10 -181.92 386.21  1.90   0.11</t>
+  </si>
+  <si>
+    <t>245678 12 -179.39 386.21  1.90   0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Term codes: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">             ALTI    DIST_COURS_EAU           EXPO_NS          NB_FECES             PENTE PROP_PRAIRIES_500 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                1                 2                 3                 4                 5                 6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">         REC_ARBO               STC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                7                 8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model-averaged coefficients:  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(full average) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)       -2.435e+00  1.795e+00   1.818e+00   1.340   0.1804  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NB_FECES           2.028e-01  1.500e-01   1.512e-01   1.341   0.1800  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENTE              2.687e-02  1.686e-02   1.701e-02   1.580   0.1141  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500  1.429e+00  8.882e-01   8.963e-01   1.594   0.1109  </t>
+  </si>
+  <si>
+    <t>REC_ARBO          -1.973e-02  8.884e-03   9.004e-03   2.191   0.0284 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFI              5.614e-02  1.490e+00   1.509e+00   0.037   0.9703  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFR              1.613e+00  1.562e+00   1.582e+00   1.019   0.3081  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCMTF             5.311e-01  1.517e+00   1.537e+00   0.346   0.7296  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCT              -4.100e-01  1.527e+00   1.547e+00   0.265   0.7911  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS           -2.731e-02  1.052e-01   1.060e-01   0.258   0.7968  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI               8.302e-05  4.062e-04   4.099e-04   0.203   0.8395  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU    -8.280e-05  4.040e-04   4.076e-04   0.203   0.8390  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(conditional average) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)       -2.4348408  1.7952417   1.8176206   1.340   0.1804  </t>
+  </si>
+  <si>
+    <t>NB_FECES           0.2428017  0.1313095   0.1329515   1.826   0.0678 .</t>
+  </si>
+  <si>
+    <t>PENTE              0.0300765  0.0148902   0.0150727   1.995   0.0460 *</t>
+  </si>
+  <si>
+    <t>PROP_PRAIRIES_500  1.6066949  0.7755715   0.7859151   2.044   0.0409 *</t>
+  </si>
+  <si>
+    <t>REC_ARBO          -0.0197275  0.0088840   0.0090036   2.191   0.0284 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFI              0.0561360  1.4896509   1.5093468   0.037   0.9703  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFR              1.6125326  1.5616123   1.5822195   1.019   0.3081  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCMTF             0.5311220  1.5166204   1.5366615   0.346   0.7296  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCT              -0.4099662  1.5271450   1.5474786   0.265   0.7911  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS           -0.2117546  0.2163960   0.2193786   0.965   0.3344  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI               0.0007777  0.0010029   0.0010167   0.765   0.4443  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU    -0.0007763  0.0009959   0.0010096   0.769   0.4419  </t>
+  </si>
+  <si>
+    <t>---</t>
+  </si>
+  <si>
+    <t>Signif. codes:  0 ‘***’ 0.001 ‘**’ 0.01 ‘*’ 0.05 ‘.’ 0.1 ‘ ’ 1</t>
+  </si>
+  <si>
+    <t>en ajoutant la distance aux lisières :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lme.formula(fixed = logit_AMOYj ~ &lt;6 unique rhs&gt;, data = info_placette_aldous_glmm, random = ~1 | ZONE2, </t>
+  </si>
+  <si>
+    <t>13467  11 -179.34 383.55  0.00   0.30</t>
+  </si>
+  <si>
+    <t>34567  11 -179.72 384.31  0.76   0.20</t>
+  </si>
+  <si>
+    <t>134567 12 -178.82 385.07  1.52   0.14</t>
+  </si>
+  <si>
+    <t>123467 12 -178.93 385.30  1.74   0.12</t>
+  </si>
+  <si>
+    <t>4567   10 -181.49 385.34  1.78   0.12</t>
+  </si>
+  <si>
+    <t>1367   10 -181.57 385.50  1.95   0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     DIST_LISIERE           EXPO_NS          NB_FECES             PENTE PROP_PRAIRIES_500          REC_ARBO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">              STC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                   Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)       -1.779599   1.734961    1.755694   1.014   0.3108  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_LISIERE      -0.001940   0.001844    0.001855   1.046   0.2955  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NB_FECES           0.249909   0.156665    0.157878   1.583   0.1134  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENTE              0.026889   0.016679    0.016823   1.598   0.1100  </t>
+  </si>
+  <si>
+    <t>REC_ARBO          -0.019620   0.008845    0.008964   2.189   0.0286 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFI             -0.051533   1.460108    1.479695   0.035   0.9722  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFR              1.493348   1.531981    1.552455   0.962   0.3361  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCMTF             0.384862   1.485503    1.505382   0.256   0.7982  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCT              -0.578254   1.506511    1.526640   0.379   0.7049  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500  0.654107   0.920661    0.925193   0.707   0.4796  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS           -0.023032   0.096616    0.097418   0.236   0.8131  </t>
+  </si>
+  <si>
+    <t>DIST_LISIERE      -0.002879   0.001530    0.001550   1.858   0.0632 .</t>
+  </si>
+  <si>
+    <t>NB_FECES           0.284623   0.134435    0.136042   2.092   0.0364 *</t>
+  </si>
+  <si>
+    <t>PENTE              0.030291   0.014503    0.014688   2.062   0.0392 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500  1.405298   0.874865    0.885078   1.588   0.1123  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS           -0.184968   0.212160    0.215084   0.860   0.3898  </t>
+  </si>
+  <si>
+    <t>en remplaçant la proportion de prairies par la distance aux lisières :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lme.formula(fixed = logit_AMOYj ~ &lt;3 unique rhs&gt;, data = info_placette_aldous_glmm, random = ~1 | ZONE2, </t>
+  </si>
+  <si>
+    <t>13456  11 -179.34 383.55  0.00   0.56</t>
+  </si>
+  <si>
+    <t>123456 12 -178.93 385.30  1.74   0.23</t>
+  </si>
+  <si>
+    <t>1356   10 -181.57 385.50  1.95   0.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_LISIERE      EXPO_NS     NB_FECES        PENTE     REC_ARBO          STC </t>
+  </si>
+  <si>
+    <t xml:space="preserve">           1            2            3            4            5            6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">              Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)  -1.242786   1.563065    1.584241   0.784   0.4328  </t>
+  </si>
+  <si>
+    <t>DIST_LISIERE -0.003066   0.001429    0.001448   2.118   0.0342 *</t>
+  </si>
+  <si>
+    <t>NB_FECES      0.311382   0.131450    0.133066   2.340   0.0193 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENTE         0.022556   0.017155    0.017282   1.305   0.1918  </t>
+  </si>
+  <si>
+    <t>REC_ARBO     -0.019349   0.008905    0.009025   2.144   0.0320 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFI        -0.220403   1.434980    1.454521   0.152   0.8796  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFR         1.304066   1.506143    1.526631   0.854   0.3930  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCMTF        0.203173   1.457438    1.477259   0.138   0.8906  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCT         -0.766601   1.481155    1.501334   0.511   0.6096  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS      -0.043088   0.128836    0.129961   0.332   0.7402  </t>
+  </si>
+  <si>
+    <t>PENTE         0.028557   0.014186    0.014380   1.986   0.0470 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS      -0.184968   0.212160    0.215084   0.860   0.3898  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">model.avg(object = model_logit_dredge_het, subset = delta &lt;= </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     ZONE2, method = ML, na.action = na.fail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                1                 2                 3                 4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                   Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                 Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)   </t>
+  </si>
+  <si>
+    <t>model.avg(object = model_log_dredge_feu, subset = delta &lt;= 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lme.formula(fixed = logit_AMOYj ~ &lt;7 unique rhs&gt;, data = info_placette_aldous_glmm_feu, random = ~1 | </t>
+  </si>
+  <si>
+    <t xml:space="preserve">      df logLik   AICc delta weight</t>
+  </si>
+  <si>
+    <t>345    6 -78.56 171.38  0.00   0.26</t>
+  </si>
+  <si>
+    <t>2345   7 -77.64 172.39  1.01   0.16</t>
+  </si>
+  <si>
+    <t>34     5 -80.43 172.44  1.05   0.15</t>
+  </si>
+  <si>
+    <t>234    6 -79.32 172.92  1.53   0.12</t>
+  </si>
+  <si>
+    <t>1234   7 -77.93 172.98  1.59   0.12</t>
+  </si>
+  <si>
+    <t>1345   7 -78.07 173.24  1.86   0.10</t>
+  </si>
+  <si>
+    <t>12345  8 -76.60 173.32  1.93   0.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          ALTI DIST_COURS_EAU   DIST_LISIERE        EXPO_NS       NB_FECES </t>
+  </si>
+  <si>
+    <t xml:space="preserve">             1              2              3              4              5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)    -1.9392216  1.1325328   1.1585737   1.674   0.0942 . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_LISIERE   -0.0086207  0.0033958   0.0035086   2.457   0.0140 * </t>
+  </si>
+  <si>
+    <t>EXPO_NS        -0.9952109  0.3521391   0.3636006   2.737   0.0062 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NB_FECES        0.2240501  0.2403900   0.2442102   0.917   0.3589   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU -0.0012940  0.0017952   0.0018234   0.710   0.4779   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI            0.0005861  0.0011896   0.0012086   0.485   0.6277   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)    -1.939222   1.132533    1.158574   1.674   0.0942 . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_LISIERE   -0.008621   0.003396    0.003509   2.457   0.0140 * </t>
+  </si>
+  <si>
+    <t>EXPO_NS        -0.995211   0.352139    0.363601   2.737   0.0062 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NB_FECES        0.365869   0.206103    0.213311   1.715   0.0863 . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU -0.002646   0.001736    0.001795   1.474   0.1404   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI            0.001857   0.001457    0.001506   1.233   0.2175   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     random = ~1 | ZONE2, method = ML, na.action = na.fail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              ALTI     DIST_COURS_EAU           NB_FECES  PROP_PRAIRIES_500 rec_myrtille_phyto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                 1                  2                  3                  4                  5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">gls(model = AMOYj ~ &lt;3 unique rhs&gt;, data = info_placette_aldous_glmm_het, correlation = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     corExp(form = ~X_L93 + Y_L93, nugget = TRUE), method = ML, na.action = na.fail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     df  logLik   AICc delta weight</t>
+  </si>
+  <si>
+    <t>134  12 -182.49 399.05  0.00   0.52</t>
+  </si>
+  <si>
+    <t>1234 13 -181.03 400.19  1.14   0.29</t>
+  </si>
+  <si>
+    <t>14   11 -185.39 401.04  1.98   0.19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">             ALTI          NB_FECES PROP_PRAIRIES_500             ZONE2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                         Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)    </t>
+  </si>
+  <si>
+    <t>(Intercept)             148.30447   35.79744    36.96210   4.012 6.01e-05 ***</t>
+  </si>
+  <si>
+    <t>ALTI                     -0.14619    0.03734     0.03861   3.786 0.000153 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500        28.80233   19.92514    20.29183   1.419 0.155781    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDE_OUEST       -8.09109   12.62309    13.07430   0.619 0.536012    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDES_EST         2.88664   13.24063    13.70629   0.211 0.833194    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU             51.32708   15.98892    16.51251   3.108 0.001881 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_NORD  -3.76708   13.48630    13.96569   0.270 0.787362    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_SUD   57.27574   22.32703    23.09192   2.480 0.013126 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2VIADENE            -23.80964   13.67204    14.10658   1.688 0.091442 .  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NB_FECES                  1.07230    2.00022     2.02298   0.530 0.596072    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500        35.62791   15.74528    16.31429   2.184 0.028973 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NB_FECES                  3.66633    2.04180     2.11710   1.732 0.083315 . </t>
+  </si>
+  <si>
+    <t>gls, sans logit avec ZONE2 en effet fixe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lm(formula = AMOYj ~ ALTI + NB_FECES + PROP_PRAIRIES_500 + ZONE2 + </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    1, data = info_placette_aldous_glmm_het, na.action = "na.fail")</t>
+  </si>
+  <si>
+    <t>Residuals:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    Min      1Q  Median      3Q     Max </t>
+  </si>
+  <si>
+    <t xml:space="preserve">-28.286  -9.811  -1.219   5.559  42.585 </t>
+  </si>
+  <si>
+    <t>Coefficients:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                         Estimate Std. Error t value Pr(&gt;|t|)    </t>
+  </si>
+  <si>
+    <t>(Intercept)             131.47644   32.21694   4.081 0.000257 ***</t>
+  </si>
+  <si>
+    <t>ALTI                     -0.12992    0.03455  -3.761 0.000639 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NB_FECES                  4.37326    1.99672   2.190 0.035464 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500        35.27494   14.68526   2.402 0.021912 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDE_OUEST       -8.62305   12.11919  -0.712 0.481616    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDES_EST        -0.80602   12.62294  -0.064 0.949461    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU             40.42401   15.15690   2.667 0.011632 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_NORD  -5.89442   11.94760  -0.493 0.624933    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_SUD   47.15155   21.35612   2.208 0.034100 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2VIADENE            -26.50106   11.40811  -2.323 0.026296 *  </t>
+  </si>
+  <si>
+    <t>Residual standard error: 16.94 on 34 degrees of freedom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multiple R-squared:  0.561,     Adjusted R-squared:  0.4448 </t>
+  </si>
+  <si>
+    <t>F-statistic: 4.827 on 9 and 34 DF,  p-value: 0.0003462</t>
+  </si>
+  <si>
+    <t>lme avec ZONE2 en effet aléatoire</t>
+  </si>
+  <si>
+    <t>lmer avec ZONE2 en effet aléatoire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">     na.fail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      df  logLik   AICc delta weight</t>
+  </si>
+  <si>
+    <t>avec ZONE2 en effet fixe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lme.formula(fixed = AMOYj ~ &lt;5 unique rhs&gt;, data = info_placette_aldous_glmm_het, random </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     = ~1 | ZONE2, method = ML, na.action = na.fail)</t>
+  </si>
+  <si>
+    <t>13    5 -193.35 398.28  0.00   0.30</t>
+  </si>
+  <si>
+    <t>134   6 -192.09 398.45  0.16   0.28</t>
+  </si>
+  <si>
+    <t>3     4 -195.14 399.30  1.02   0.18</t>
+  </si>
+  <si>
+    <t>1345  7 -191.53 400.17  1.88   0.12</t>
+  </si>
+  <si>
+    <t>1234  7 -191.53 400.17  1.89   0.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)        75.306152  41.735589   42.478379   1.773  0.07626 . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI               -0.065283   0.042257    0.042890   1.522  0.12798   </t>
+  </si>
+  <si>
+    <t>NB_FECES            6.090547   2.102455    2.177004   2.798  0.00515 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500  14.267586  17.540718   17.787902   0.802  0.42250   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_myrtille_phyto -0.056053   0.223057    0.227585   0.246  0.80545   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU      0.002341   0.009227    0.009411   0.249  0.80354   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)        75.30615   41.73559    42.47838   1.773  0.07626 . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI               -0.07981    0.03199     0.03300   2.418  0.01560 * </t>
+  </si>
+  <si>
+    <t>NB_FECES            6.09055    2.10246     2.17700   2.798  0.00515 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500  27.69769   15.01035    15.56481   1.780  0.07516 . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_myrtille_phyto -0.47407    0.47183     0.48978   0.968  0.33309   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU      0.01987    0.01935     0.02008   0.989  0.32245   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">lmer(formula = AMOYj ~ &lt;5 unique rhs&gt;, data = info_placette_aldous_glmm_het, REML = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     FALSE, na.action = na.fail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)        75.306118  40.815096   41.429527   1.818  0.06911 . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI               -0.065283   0.041476    0.041997   1.554  0.12007   </t>
+  </si>
+  <si>
+    <t>NB_FECES            6.090548   2.019005    2.082719   2.924  0.00345 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500  14.267579  17.206210   17.407513   0.820  0.41243   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_myrtille_phyto -0.056053   0.216248    0.219924   0.255  0.79882   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU      0.002341   0.008952    0.009100   0.257  0.79699   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)        75.30612   40.81510    41.42953   1.818  0.06911 . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI               -0.07981    0.03072     0.03157   2.528  0.01147 * </t>
+  </si>
+  <si>
+    <t>NB_FECES            6.09055    2.01900     2.08272   2.924  0.00345 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500  27.69768   14.23893    14.70625   1.883  0.05965 . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_myrtille_phyto -0.47407    0.44422     0.45923   1.032  0.30192   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU      0.01987    0.01822     0.01883   1.055  0.29131   </t>
+  </si>
+  <si>
+    <t>gls, avec ZONE2 en effet fixe et integré comme variable de nichage dans la structure d'autocorrélation spatiale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gls(model = AMOYj ~ &lt;4 unique rhs&gt;, data = info_placette_aldous_glmm_het, correlation = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     corExp(form = ~X_L93 + Y_L93 | ZONE2, nugget = TRUE), method = ML, na.action = na.fail)</t>
+  </si>
+  <si>
+    <t>134  12 -182.88 399.82  0.00   0.34</t>
+  </si>
+  <si>
+    <t>1234 13 -181.09 400.32  0.50   0.26</t>
+  </si>
+  <si>
+    <t>2     5 -194.43 400.44  0.63   0.25</t>
+  </si>
+  <si>
+    <t>12    6 -193.52 401.31  1.50   0.16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                         Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)</t>
+  </si>
+  <si>
+    <t>(Intercept)              94.96458   61.62117    62.08274   1.530    0.126</t>
+  </si>
+  <si>
+    <t>ALTI                     -0.08756    0.06924     0.06969   1.256    0.209</t>
+  </si>
+  <si>
+    <t>PROP_PRAIRIES_500        21.75013   21.58726    21.83407   0.996    0.319</t>
+  </si>
+  <si>
+    <t>ZONE2BORALDE_OUEST       -4.24519   10.22247    10.54808   0.402    0.687</t>
+  </si>
+  <si>
+    <t>ZONE2BORALDES_EST         0.78992   10.05405    10.41260   0.076    0.940</t>
+  </si>
+  <si>
+    <t>ZONE2PLATEAU             28.68486   26.68634    26.88047   1.067    0.286</t>
+  </si>
+  <si>
+    <t>ZONE2PLATEAU_FERME_NORD  -3.11390   10.36098    10.71347   0.291    0.771</t>
+  </si>
+  <si>
+    <t>ZONE2PLATEAU_FERME_SUD   32.47793   31.75014    32.07244   1.013    0.311</t>
+  </si>
+  <si>
+    <t>ZONE2VIADENE            -16.07490   16.40288    16.61287   0.968    0.333</t>
+  </si>
+  <si>
+    <t>NB_FECES                  3.17042    2.94258     2.97755   1.065    0.287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                         Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)              94.96458   61.62117    62.08274   1.530  0.12610   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI                     -0.11600    0.05525     0.05600   2.071  0.03833 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500        36.48180   15.62713    16.19206   2.253  0.02425 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDE_OUEST       -7.12051   12.44202    12.88982   0.552  0.58066   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDES_EST         1.32494   12.99386    13.45917   0.098  0.92158   </t>
+  </si>
+  <si>
+    <t>ZONE2PLATEAU             48.11353   16.11632    16.64866   2.890  0.00385 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_NORD  -5.22298   13.00168    13.47234   0.388  0.69825   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_SUD   54.47571   22.19254    22.95671   2.373  0.01765 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2VIADENE            -26.96267   12.55890    13.01362   2.072  0.03828 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NB_FECES                  4.76892    2.32407     2.39014   1.995  0.04602 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">gls(model = AMOYj ~ &lt;5 unique rhs&gt;, data = info_placette_aldous_glmm_het, correlation = </t>
+  </si>
+  <si>
+    <t>2       5 -194.43 400.44  0.00   0.35</t>
+  </si>
+  <si>
+    <t>12      6 -193.52 401.31  0.87   0.23</t>
+  </si>
+  <si>
+    <t>24      6 -194.02 402.31  1.86   0.14</t>
+  </si>
+  <si>
+    <t>23      6 -194.02 402.32  1.88   0.14</t>
+  </si>
+  <si>
+    <t>(Null)  4 -196.66 402.34  1.89   0.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              ALTI           NB_FECES  PROP_PRAIRIES_500 rec_myrtille_phyto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                 1                  2                  3                  4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)</t>
+  </si>
+  <si>
+    <t>(Intercept)        24.184269  19.088484   19.350264   1.250    0.211</t>
+  </si>
+  <si>
+    <t>NB_FECES            4.541531   2.806953    2.854661   1.591    0.112</t>
+  </si>
+  <si>
+    <t>ALTI               -0.007333   0.017489    0.017709   0.414    0.679</t>
+  </si>
+  <si>
+    <t>rec_myrtille_phyto -0.055793   0.217653    0.221615   0.252    0.801</t>
+  </si>
+  <si>
+    <t>PROP_PRAIRIES_500   2.093262   8.166288    8.314246   0.252    0.801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)        24.18427   19.08848    19.35026   1.250   0.2114  </t>
+  </si>
+  <si>
+    <t>NB_FECES            5.26541    2.30723     2.37412   2.218   0.0266 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI               -0.03195    0.02337     0.02408   1.327   0.1845  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_myrtille_phyto -0.39949    0.44933     0.46299   0.863   0.3882  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500  15.07738   16.86940    17.38218   0.867   0.3857 </t>
+  </si>
+  <si>
+    <t>gls avec ZONE2 en variable de nichage pour l'autocorrélation spatiale seulement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lme.formula(fixed = AMOYj ~ &lt;6 unique rhs&gt;, data = info_placette_aldous_phyto_glmm_feu, </t>
+  </si>
+  <si>
+    <t>12345  8 -208.66 436.92  0.00   0.27</t>
+  </si>
+  <si>
+    <t>1345   7 -210.19 437.12  0.20   0.24</t>
+  </si>
+  <si>
+    <t>126    8 -209.34 438.29  1.37   0.14</t>
+  </si>
+  <si>
+    <t>1235   7 -210.86 438.44  1.52   0.13</t>
+  </si>
+  <si>
+    <t>345    6 -212.28 438.56  1.64   0.12</t>
+  </si>
+  <si>
+    <t>1234   7 -211.02 438.77  1.85   0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">             ALTI    DIST_COURS_EAU      DIST_LISIERE           EXPO_NS rec_roncier_phyto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                1                 2                 3                 4                 5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)        5.99066   18.88256    19.28794   0.311   0.7561  </t>
+  </si>
+  <si>
+    <t>ALTI               0.03410    0.02027     0.02065   1.651   0.0987 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU    -0.02749    0.02732     0.02767   0.994   0.3204  </t>
+  </si>
+  <si>
+    <t>DIST_LISIERE      -0.10313    0.06043     0.06127   1.683   0.0923 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS           -6.99076    5.56597     5.63593   1.240   0.2148  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_roncier_phyto -0.19034    0.15036     0.15268   1.247   0.2125  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFR              6.72687   18.27437    18.35786   0.366   0.7140  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCMTF             1.34389    4.09511     4.13787   0.325   0.7453  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCT               0.23783    2.94863     3.04160   0.078   0.9377  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)        5.99066   18.88256    19.28794   0.311  0.75611   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI               0.03870    0.01698     0.01750   2.212  0.02696 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU    -0.04313    0.02229     0.02295   1.880  0.06013 . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_LISIERE      -0.11932    0.04788     0.04910   2.430  0.01510 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS           -9.46510    4.30411     4.42565   2.139  0.03246 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_roncier_phyto -0.25128    0.12056     0.12434   2.021  0.04329 * </t>
+  </si>
+  <si>
+    <t>STCFR             49.56759   18.36434    18.96804   2.613  0.00897 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCMTF             9.90261    6.23033     6.43514   1.539  0.12384   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCT               1.75245    7.83653     8.09415   0.217  0.82859   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">lmer(formula = AMOYj ~ &lt;6 unique rhs&gt;, data = info_placette_aldous_phyto_glmm_feu, REML </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     = FALSE, na.action = na.fail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)        5.99066   18.18031    18.52689   0.323   0.7464  </t>
+  </si>
+  <si>
+    <t>ALTI               0.03410    0.01961     0.01994   1.711   0.0872 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU    -0.02749    0.02672     0.02701   1.018   0.3087  </t>
+  </si>
+  <si>
+    <t>DIST_LISIERE      -0.10313    0.05905     0.05976   1.726   0.0844 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS           -6.99076    5.45043     5.50952   1.269   0.2045  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_roncier_phyto -0.19034    0.14654     0.14851   1.282   0.1999  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFR              6.72687   18.12038    18.18865   0.370   0.7115  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCMTF             1.34389    4.01558     4.05095   0.332   0.7401  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCT               0.23783    2.77018     2.85049   0.083   0.9335  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)        5.99066   18.18031    18.52689   0.323  0.74643   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI               0.03870    0.01608     0.01653   2.342  0.01919 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU    -0.04313    0.02110     0.02167   1.990  0.04654 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_LISIERE      -0.11932    0.04585     0.04690   2.544  0.01096 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS           -9.46510    4.09903     4.20463   2.251  0.02438 * </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_roncier_phyto -0.25128    0.11417     0.11749   2.139  0.03245 * </t>
+  </si>
+  <si>
+    <t>STCFR             49.56759   17.20329    17.72622   2.796  0.00517 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCMTF             9.90261    5.83643     6.01384   1.647  0.09963 . </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCT               1.75245    7.34108     7.56423   0.232  0.81679   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">lm(formula = AMOYj ~ &lt;6 unique rhs&gt;, data = info_placette_aldous_phyto_glmm_feu, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     na.action = na.fail)</t>
+  </si>
+  <si>
+    <t>1267   12 -201.78 436.23  0.00   0.27</t>
+  </si>
+  <si>
+    <t>127     9 -206.88 436.37  0.14   0.25</t>
+  </si>
+  <si>
+    <t>12567  13 -200.66 437.73  1.50   0.13</t>
+  </si>
+  <si>
+    <t>1247   10 -206.00 437.79  1.56   0.12</t>
+  </si>
+  <si>
+    <t>1257   10 -206.09 437.98  1.74   0.11</t>
+  </si>
+  <si>
+    <t>123457 12 -202.71 438.09  1.86   0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">              STC             ZONE2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                6                 7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                        Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)             11.26689   14.41284    14.84191   0.759  0.44778    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI                     0.04518    0.01899     0.01952   2.315  0.02064 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU          -0.05595    0.02203     0.02268   2.467  0.01363 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFR                   19.19155   26.20137    26.37545   0.728  0.46684    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCMTF                   4.31836    6.64539     6.72730   0.642  0.52093    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCT                    -0.37548    5.04903     5.21444   0.072  0.94260    </t>
+  </si>
+  <si>
+    <t>ZONE2BORALDE_OUEST     -30.68844    8.85634     9.10425   3.371  0.00075 ***</t>
+  </si>
+  <si>
+    <t>ZONE2BORALDES_EST      -28.16858    6.61055     6.79137   4.148 3.36e-05 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU             1.75266   15.76554    16.21606   0.108  0.91393    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_SUD -32.27936   20.70106    21.29335   1.516  0.12954    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2VIADENE           -33.66463   19.05718    19.62709   1.715  0.08631 .  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_roncier_phyto       -0.05756    0.10652     0.10799   0.533  0.59402    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS                 -1.41404    3.30447     3.34329   0.423  0.67233    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_LISIERE            -0.01062    0.03452     0.03477   0.306  0.75997    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFR                   47.88659   18.40845    19.01864   2.518  0.01181 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCMTF                  10.77513    6.37325     6.58417   1.637  0.10173    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCT                    -0.93689    7.94249     8.20483   0.114  0.90909    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_roncier_phyto       -0.16445    0.12182     0.12545   1.311  0.18991    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS                 -6.09250    4.30628     4.43351   1.374  0.16938    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_LISIERE            -0.09882    0.04870     0.05031   1.964  0.04949 *  </t>
+  </si>
+  <si>
+    <t>lm avec effet fixe sur ZONE2</t>
+  </si>
+  <si>
+    <t>gls avec effet fixe sur ZONE2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gls(model = AMOYj ~ &lt;3 unique rhs&gt;, data = info_placette_aldous_phyto_glmm_feu, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">     correlation = corExp(form = ~X_L93 + Y_L93, nugget = TRUE), method = ML, na.action = </t>
+  </si>
+  <si>
+    <t>235   7 -211.53 439.79  0.00   0.47</t>
+  </si>
+  <si>
+    <t>2345  8 -210.63 440.86  1.06   0.28</t>
+  </si>
+  <si>
+    <t>1235  8 -210.75 441.09  1.30   0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   DIST_COURS_EAU      DIST_LISIERE           EXPO_NS          REC_ARBO rec_roncier_phyto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                    Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)    </t>
+  </si>
+  <si>
+    <t>(Intercept)        37.784815  10.894514   11.111971   3.400 0.000673 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_LISIERE       -0.140617   0.042951    0.044131   3.186 0.001441 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS           -12.449324   4.375721    4.496781   2.768 0.005632 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_roncier_phyto  -0.287152   0.116578    0.119818   2.397 0.016550 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REC_ARBO           -0.049111   0.105697    0.107024   0.459 0.646323    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU     -0.007002   0.016248    0.016451   0.426 0.670377    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                   Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)    </t>
+  </si>
+  <si>
+    <t>(Intercept)        37.78482   10.89451    11.11197   3.400 0.000673 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_LISIERE       -0.14062    0.04295     0.04413   3.186 0.001441 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS           -12.44932    4.37572     4.49678   2.768 0.005632 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_roncier_phyto  -0.28715    0.11658     0.11982   2.397 0.016549 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REC_ARBO           -0.17638    0.13295     0.13671   1.290 0.196982    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU     -0.02825    0.02156     0.02217   1.274 0.202640    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">gls(model = AMOYj ~ &lt;2 unique rhs&gt;, data = info_placette_aldous_glmm_het, correlation = </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    df  logLik   AICc delta weight</t>
+  </si>
+  <si>
+    <t>12   7 -190.50 398.11  0.00   0.62</t>
+  </si>
+  <si>
+    <t>134 12 -182.49 399.05  0.95   0.38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">             ALTI         FREQ_CERF PROP_PRAIRIES_500             ZONE2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                               Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)  </t>
+  </si>
+  <si>
+    <t>(Intercept)                    94.82843   49.79354    50.29316   1.886   0.0594 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI                           -0.08825    0.05464     0.05512   1.601   0.1094  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREQ_CERFFréquentation moyenne 15.21429   13.13086    13.19860   1.153   0.2490  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREQ_CERFFréquentation forte   27.14624   23.56543    23.69419   1.146   0.2519  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500              13.78123   20.08907    20.26747   0.680   0.4965  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDE_OUEST             -3.11819    8.73612     8.98575   0.347   0.7286  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDES_EST               1.38934    8.28638     8.56978   0.162   0.8712  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU                   20.93871   28.10896    28.22098   0.742   0.4581  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_NORD        -1.43642    8.57804     8.87145   0.162   0.8714  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_SUD         23.29655   32.40189    32.60252   0.715   0.4749  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2VIADENE                   -9.94165   15.01206    15.17322   0.655   0.5123  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)                     94.82843   49.79354    50.29316   1.886 0.059361 .  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI                            -0.08825    0.05464     0.05512   1.601 0.109371    </t>
+  </si>
+  <si>
+    <t>FREQ_CERFFréquentation moyenne  24.69589    6.76130     6.97212   3.542 0.000397 ***</t>
+  </si>
+  <si>
+    <t>FREQ_CERFFréquentation forte    44.06388   12.48825    12.87763   3.422 0.000622 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500               35.89475   16.04324    16.61740   2.160 0.030767 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDE_OUEST              -8.12168   12.57565    13.02571   0.624 0.532949    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDES_EST                3.61869   13.06814    13.53582   0.267 0.789206    </t>
+  </si>
+  <si>
+    <t>ZONE2PLATEAU                    54.53722   15.01902    15.55653   3.506 0.000455 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_NORD         -3.74131   13.52891    14.01308   0.267 0.789479    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_SUD          60.67848   21.59299    22.36576   2.713 0.006668 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2VIADENE                   -25.89413   13.18731    13.65926   1.896 0.057997 .  </t>
+  </si>
+  <si>
+    <t>gls avec distance aux lisieres et remplacement nb_feces par freq_cerf</t>
+  </si>
+  <si>
+    <t>gls sans distance aux lisières et en remplaçant nb_feces par freq_cerf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gls(model = AMOYj ~ &lt;8 unique rhs&gt;, data = info_placette_aldous_phyto_glmm_feu, </t>
+  </si>
+  <si>
+    <t>3467  10 -208.18 442.15  0.00   0.21</t>
+  </si>
+  <si>
+    <t>347    9 -209.97 442.56  0.42   0.17</t>
+  </si>
+  <si>
+    <t>128   11 -206.74 442.62  0.47   0.16</t>
+  </si>
+  <si>
+    <t>23467 11 -206.91 442.95  0.81   0.14</t>
+  </si>
+  <si>
+    <t>1278  14 -201.72 443.79  1.65   0.09</t>
+  </si>
+  <si>
+    <t>34567 11 -207.44 444.01  1.86   0.08</t>
+  </si>
+  <si>
+    <t>2467  10 -209.14 444.07  1.92   0.08</t>
+  </si>
+  <si>
+    <t>47     8 -212.27 444.13  1.99   0.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">             ALTI    DIST_COURS_EAU           EXPO_NS PROP_PRAIRIES_500          REC_ARBO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_roncier_phyto               STC             ZONE2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                6                 7                 8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                       Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)             5.14621   11.69565    11.96802   0.430   0.6672  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS                -5.61544    5.81852     5.88023   0.955   0.3396  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500      28.55226   21.84421    22.08768   1.293   0.1961  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_roncier_phyto      -0.11479    0.14049     0.14191   0.809   0.4186  </t>
+  </si>
+  <si>
+    <t>STCFR                  58.27645   32.21807    32.52595   1.792   0.0732 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCMTF                  4.65504    6.71538     6.88096   0.677   0.4987  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCT                    2.72294    7.95428     8.17430   0.333   0.7391  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI                    0.01184    0.02254     0.02266   0.523   0.6012  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU         -0.02266    0.02951     0.02974   0.762   0.4461  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDE_OUEST     -7.75417   14.13257    14.17735   0.547   0.5844  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDES_EST      -7.29200   12.96090    12.98463   0.562   0.5744  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU            0.54869    8.04842     8.27466   0.066   0.9471  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_SUD -8.45105   17.63266    17.80386   0.475   0.6350  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2VIADENE           -9.03246   18.09463    18.24524   0.495   0.6206  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REC_ARBO               -0.01303    0.05952     0.06036   0.216   0.8291  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)              5.14621   11.69565    11.96802   0.430  0.66720    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPO_NS                 -9.48766    4.52353     4.65640   2.038  0.04159 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROP_PRAIRIES_500       38.23370   16.39542    16.82655   2.272  0.02307 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_roncier_phyto       -0.22807    0.11568     0.11907   1.915  0.05544 .  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCFR                   69.60805   21.23838    21.79170   3.194  0.00140 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCMTF                   5.56019    6.98802     7.17784   0.775  0.43856    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STCT                     3.25240    8.59368     8.83684   0.368  0.71284    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI                     0.04677    0.01933     0.01985   2.356  0.01847 *  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU          -0.04828    0.02488     0.02545   1.897  0.05784 .  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2BORALDE_OUEST     -30.62258    9.40624     9.66869   3.167  0.00154 ** </t>
+  </si>
+  <si>
+    <t>ZONE2BORALDES_EST      -28.79740    6.64097     6.82156   4.222 2.43e-05 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU             2.16686   15.88427    16.33689   0.133  0.89448    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2PLATEAU_FERME_SUD -33.37467   19.90035    20.49345   1.629  0.10341    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZONE2VIADENE           -35.67075   18.51525    19.09002   1.869  0.06168 .  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REC_ARBO                -0.16039    0.14138     0.14567   1.101  0.27087    </t>
+  </si>
+  <si>
+    <t>gls en enlevant dist_lisiere</t>
+  </si>
+  <si>
+    <t>gls en enlevant prop_prairies_500</t>
+  </si>
+  <si>
+    <t>Generalized least squares fit by maximum likelihood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Model: AMOYj ~ ALTI + FREQ_CERF + 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Data: info_placette_aldous_glmm_het </t>
+  </si>
+  <si>
+    <t>Correlation Structure: Exponential spatial correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Formula: ~X_L93 + Y_L93 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Parameter estimate(s):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       range       nugget </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.196345e+02 1.163927e-06 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Correlation: </t>
+  </si>
+  <si>
+    <r>
+      <t>Avis : abbreviate utilisé avec des caractères non ASCII</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Lucida Console"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">                               (Intr) ALTI   FREQ_m</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTI                           -0.981              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREQ_CERFFréquentation moyenne  0.316 -0.445       </t>
+  </si>
+  <si>
+    <t>FREQ_CERFFréquentation forte    0.236 -0.307  0.339</t>
+  </si>
+  <si>
+    <t>Standardized residuals:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       Min         Q1        Med         Q3        Max </t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.6780901 -0.6118169 -0.3148761  0.3681701  3.1654612 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual standard error: 18.36975 </t>
+  </si>
+  <si>
+    <t>Degrees of freedom: 44 total; 40 residual</t>
+  </si>
+  <si>
+    <t>gls en remplaçant prop_prairies_500 par distance_lisiere</t>
+  </si>
+  <si>
+    <t>23   7 -187.22 391.56  0.00   0.73</t>
+  </si>
+  <si>
+    <t>123  8 -186.69 393.50  1.95   0.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU      FREQ_CERF          PENTE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">             1              2              3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)                     0.077492   5.938800    6.091816   0.013 0.989851    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREQ_CERFFréquentation moyenne 18.368326   5.641161    5.818279   3.157 0.001594 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREQ_CERFFréquentation forte   19.535538  11.737648   12.105393   1.614 0.106573    </t>
+  </si>
+  <si>
+    <t>PENTE                           0.977887   0.265862    0.273931   3.570 0.000357 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU                  0.004353   0.011089    0.011300   0.385 0.700051    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                               Estimate Std. Error Adjusted SE z value Pr(&gt;|z|)    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)                     0.07749    5.93880     6.09182   0.013 0.989851    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREQ_CERFFréquentation moyenne 18.36833    5.64116     5.81828   3.157 0.001594 ** </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FREQ_CERFFréquentation forte   19.53554   11.73765    12.10539   1.614 0.106573    </t>
+  </si>
+  <si>
+    <t>PENTE                           0.97789    0.26586     0.27393   3.570 0.000357 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIST_COURS_EAU                  0.01588    0.01629     0.01682   0.944 0.345122    </t>
+  </si>
+  <si>
+    <t>gls en ajoutant la pente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   df  logLik   AICc delta weight</t>
+  </si>
+  <si>
+    <t>1   6 -193.58 401.43     0   0.73</t>
+  </si>
+  <si>
+    <t>12  7 -193.16 403.43     2   0.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         FREQ_CERF rec_myrtille_phyto </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                 1                  2 </t>
+  </si>
+  <si>
+    <t>(Intercept)                     11.2807     4.6553      4.7969   2.352   0.0187 *</t>
+  </si>
+  <si>
+    <t>FREQ_CERFFréquentation moyenne  15.4944     6.5728      6.7738   2.287   0.0222 *</t>
+  </si>
+  <si>
+    <t>FREQ_CERFFréquentation forte    33.6471    13.0570     13.4563   2.500   0.0124 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_myrtille_phyto              -0.1162     0.3184      0.3248   0.358   0.7205  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">rec_myrtille_phyto              -0.4318     0.4904      0.5057   0.854   0.3931  </t>
+  </si>
+  <si>
+    <t>gls en enlevant pente et altitude</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -261,13 +1727,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Console"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC5060B"/>
+      <name val="Lucida Console"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -282,12 +1766,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -622,6 +2120,4496 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAF2A5D-A54C-46E5-BD11-BF34B7EEB505}">
+  <dimension ref="A1:A158"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="135.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="3"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="3"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="3"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="3"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="3"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="3"/>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="3"/>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="3"/>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="3"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C6FA983-C7D8-4065-97FB-B0D1853D6E26}">
+  <dimension ref="A1:A448"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="119.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3"/>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="4"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="3"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="3"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="3"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="3"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="3"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="3"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="3"/>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="3"/>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="3"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="3"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="3"/>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="3"/>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="3"/>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="3"/>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="1" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="3"/>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" s="3"/>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" s="3"/>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" s="3"/>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" s="4" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" s="4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A246" s="4" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A247" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" s="3"/>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258" s="3"/>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263" s="3"/>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267" s="3"/>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288" s="4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290" s="4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292" s="4" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295" s="4" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" s="3"/>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308" s="3"/>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A312" s="4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A313" s="3"/>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315" s="4" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317" s="3"/>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321" s="4" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322" s="4" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323" s="4" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325" s="4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326" s="4" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327" s="4" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328" s="4" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329" s="4" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330" s="4" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335" s="4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336" s="4" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337" s="4" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338" s="4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339" s="4" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340" s="4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341" s="4" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342" s="4" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343" s="4" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344" s="4" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345" s="4" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350" s="1" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351" s="4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352" s="4" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353" s="4" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354" s="3"/>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355" s="4" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356" s="4" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357" s="4" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358" s="4" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359" s="4" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360" s="3"/>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361" s="4" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362" s="3"/>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363" s="4" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364" s="7" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365" s="5" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366" s="5" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367" s="5" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368" s="6"/>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369" s="5" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A370" s="5" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A371" s="5" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A372" s="6"/>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A373" s="5" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A374" s="5" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A377" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A378" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A379" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A380" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A381" s="3"/>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A382" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A383" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A384" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A385" s="3"/>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A386" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A387" s="4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A388" s="4" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A389" s="4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A390" s="3"/>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A391" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A392" s="4" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A393" s="4" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A394" s="3"/>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A395" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A396" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A397" s="4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A398" s="4" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A399" s="4" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A400" s="4" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A401" s="4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A402" s="4" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A403" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A404" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A405" s="4" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A406" s="4" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A407" s="4" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A408" s="4" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A409" s="4" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A410" s="4" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A411" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A412" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A415" s="1" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A416" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A417" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A418" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A419" s="3"/>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A420" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A421" s="4" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A422" s="4" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A423" s="3"/>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A424" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A425" s="4" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A426" s="4" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A427" s="4" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A428" s="3"/>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A429" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A430" s="4" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A431" s="4" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A432" s="3"/>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A433" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A434" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A435" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A436" s="4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A437" s="4" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A438" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A439" s="4" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A440" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A441" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A442" s="4" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A443" s="4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A444" s="4" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A445" s="4" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A446" s="4" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A447" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A448" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52397DC7-DE12-422B-A3F9-960C40791D8C}">
+  <dimension ref="A1:A352"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="121.140625" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="3"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="3"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="3"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="3"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="3"/>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="3"/>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="3"/>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A146" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A149" s="3"/>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A153" s="3"/>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A162" s="3"/>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A168" s="3"/>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A204" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A207" s="1" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A210" s="3"/>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A215" s="3"/>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A219" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A221" s="3"/>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A225" s="3"/>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A227" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A231" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A243" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A245" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A248" s="1" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A249" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A250" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A251" s="3"/>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A254" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A256" s="3"/>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A257" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A258" s="4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A259" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A260" s="4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A261" s="4" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A262" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A263" s="4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A264" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A265" s="4" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A267" s="3"/>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A268" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A269" s="4" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A271" s="4" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A273" s="3"/>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A274" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A275" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A277" s="4" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A278" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A279" s="4" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A280" s="4" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A281" s="4" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A282" s="4" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A283" s="4" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A284" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A285" s="4" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A286" s="4" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A287" s="4" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A288" s="4" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A289" s="4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A290" s="4" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A291" s="4" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A292" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A293" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A294" s="4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A295" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A296" s="4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A297" s="4" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A298" s="4" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A299" s="4" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A300" s="4" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A301" s="4" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A302" s="4" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A303" s="4" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A304" s="4" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A305" s="4" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A306" s="4" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A307" s="4" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A308" s="4" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A309" s="4" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A310" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A311" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A314" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A315" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A316" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A317" s="3"/>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A318" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A319" s="4" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A320" s="4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A321" s="4" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A322" s="3"/>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A323" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A324" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A325" s="4" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A326" s="4" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A327" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A328" s="3"/>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A329" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A330" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A331" s="4" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A332" s="3"/>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A333" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A334" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A335" s="4" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A336" s="4" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A337" s="4" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A338" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A339" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A340" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A341" s="4" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A342" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A343" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A344" s="4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A345" s="4" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A346" s="4" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A347" s="4" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A348" s="4" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A349" s="4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A350" s="4" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A351" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A352" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8548F4FC-2DAF-4A95-B08D-934C9CAF586B}">
   <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -632,23 +6620,23 @@
     <col min="5" max="6" width="44.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -843,10 +6831,9 @@
       <c r="D12" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="2"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -895,10 +6882,9 @@
       <c r="D16" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" t="s">
         <v>10</v>
       </c>
-      <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -913,10 +6899,9 @@
       <c r="D17" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="2"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -949,10 +6934,9 @@
       <c r="D19" t="s">
         <v>16</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" t="s">
         <v>10</v>
       </c>
-      <c r="F19" s="2"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -967,10 +6951,9 @@
       <c r="D20" t="s">
         <v>18</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" t="s">
         <v>10</v>
       </c>
-      <c r="F20" s="2"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -1070,10 +7053,9 @@
       <c r="D27" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" t="s">
         <v>10</v>
       </c>
-      <c r="F27" s="2"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
@@ -1105,10 +7087,9 @@
       <c r="D29" t="s">
         <v>16</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>10</v>
       </c>
-      <c r="F29" s="2"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
@@ -1141,12 +7122,11 @@
       <c r="D32" t="s">
         <v>3</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" t="s">
         <v>10</v>
       </c>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -1159,17 +7139,16 @@
       <c r="D33" t="s">
         <v>3</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" t="s">
         <v>10</v>
       </c>
-      <c r="F33" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD353175-068C-470E-9A5A-63003A4035D0}">
   <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1182,26 +7161,26 @@
     <col min="6" max="7" width="43.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1235,7 +7214,7 @@
       <c r="D3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1269,7 +7248,7 @@
       <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1286,7 +7265,7 @@
       <c r="D6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1388,7 +7367,7 @@
       <c r="D14" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1405,7 +7384,7 @@
       <c r="D15" t="s">
         <v>3</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1422,7 +7401,7 @@
       <c r="D16" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1439,7 +7418,7 @@
       <c r="D17" t="s">
         <v>18</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1541,7 +7520,7 @@
       <c r="D25" t="s">
         <v>3</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1709,7 +7688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FADABA78-6122-40B1-8FD2-E660E7FD5F37}">
   <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1723,26 +7702,26 @@
     <col min="7" max="7" width="81.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1793,7 +7772,7 @@
       <c r="D4" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="1"/>
@@ -1862,7 +7841,7 @@
       <c r="D9" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1879,7 +7858,7 @@
       <c r="D10" t="s">
         <v>48</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1896,7 +7875,7 @@
       <c r="D11" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1913,7 +7892,7 @@
       <c r="D12" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1930,7 +7909,7 @@
       <c r="D13" t="s">
         <v>48</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2069,7 +8048,7 @@
       <c r="D22" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2086,7 +8065,7 @@
       <c r="D23" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2103,7 +8082,7 @@
       <c r="D24" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2137,7 +8116,7 @@
       <c r="D27" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2174,7 +8153,7 @@
       <c r="D29" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2191,7 +8170,7 @@
       <c r="D30" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2225,7 +8204,7 @@
       <c r="D32" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2242,7 +8221,7 @@
       <c r="D33" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" t="s">
         <v>10</v>
       </c>
     </row>
@@ -2293,7 +8272,7 @@
       <c r="D37" t="s">
         <v>46</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" t="s">
         <v>10</v>
       </c>
     </row>
